--- a/data/resultados.xlsx
+++ b/data/resultados.xlsx
@@ -373,10 +373,10 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -384,10 +384,10 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -395,7 +395,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4">
         <v>0</v>

--- a/data/resultados.xlsx
+++ b/data/resultados.xlsx
@@ -350,7 +350,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="14.08984375" bestFit="1" customWidth="1"/>
@@ -401,6 +401,351 @@
         <v>0</v>
       </c>
     </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A53">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A54">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A55">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A56">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A57">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A58">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A59">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A61">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A62">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A63">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A64">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A65">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A66">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A67">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A68">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A69">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A70">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A71">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A72">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A73">
+        <v>72</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/resultados.xlsx
+++ b/data/resultados.xlsx
@@ -394,12 +394,6 @@
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5">
@@ -434,6 +428,12 @@
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">

--- a/data/resultados.xlsx
+++ b/data/resultados.xlsx
@@ -461,82 +461,88 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B24">
+        <v>4</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>

--- a/data/resultados.xlsx
+++ b/data/resultados.xlsx
@@ -373,7 +373,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -383,12 +383,6 @@
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4">
@@ -428,12 +422,6 @@
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">

--- a/data/resultados.xlsx
+++ b/data/resultados.xlsx
@@ -353,7 +353,7 @@
   <dimension ref="A1:C73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="14.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.26953125" customWidth="1"/>
     <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -449,88 +449,82 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24">
-        <v>4</v>
-      </c>
-      <c r="C24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>

--- a/data/resultados.xlsx
+++ b/data/resultados.xlsx
@@ -383,6 +383,12 @@
       <c r="A3">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4">

--- a/data/resultados.xlsx
+++ b/data/resultados.xlsx
@@ -429,6 +429,12 @@
       <c r="A11">
         <v>10</v>
       </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12">

--- a/data/resultados.xlsx
+++ b/data/resultados.xlsx
@@ -461,82 +461,88 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B24">
+        <v>4</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>

--- a/data/resultados.xlsx
+++ b/data/resultados.xlsx
@@ -424,6 +424,12 @@
       <c r="A10">
         <v>9</v>
       </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11">

--- a/data/resultados.xlsx
+++ b/data/resultados.xlsx
@@ -456,6 +456,12 @@
       <c r="A14">
         <v>13</v>
       </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15">

--- a/data/resultados.xlsx
+++ b/data/resultados.xlsx
@@ -467,6 +467,12 @@
       <c r="A15">
         <v>14</v>
       </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16">

--- a/data/resultados.xlsx
+++ b/data/resultados.xlsx
@@ -529,6 +529,12 @@
       <c r="A25">
         <v>24</v>
       </c>
+      <c r="B25">
+        <v>2</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26">

--- a/data/resultados.xlsx
+++ b/data/resultados.xlsx
@@ -560,6 +560,12 @@
       <c r="A30">
         <v>29</v>
       </c>
+      <c r="B30">
+        <v>7</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31">

--- a/data/resultados.xlsx
+++ b/data/resultados.xlsx
@@ -576,6 +576,12 @@
       <c r="A32">
         <v>31</v>
       </c>
+      <c r="B32">
+        <v>2</v>
+      </c>
+      <c r="C32">
+        <v>2</v>
+      </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A33">

--- a/data/resultados.xlsx
+++ b/data/resultados.xlsx
@@ -571,6 +571,12 @@
       <c r="A31">
         <v>30</v>
       </c>
+      <c r="B31">
+        <v>1</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32">

--- a/data/resultados.xlsx
+++ b/data/resultados.xlsx
@@ -589,82 +589,88 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B33">
+        <v>5</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>47</v>
       </c>

--- a/data/resultados.xlsx
+++ b/data/resultados.xlsx
@@ -624,6 +624,12 @@
       <c r="A38">
         <v>37</v>
       </c>
+      <c r="B38">
+        <v>1</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39">
@@ -654,10 +660,22 @@
       <c r="A44">
         <v>43</v>
       </c>
+      <c r="B44">
+        <v>0</v>
+      </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>44</v>
+      </c>
+      <c r="B45">
+        <v>1</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">

--- a/data/resultados.xlsx
+++ b/data/resultados.xlsx
@@ -635,6 +635,12 @@
       <c r="A39">
         <v>38</v>
       </c>
+      <c r="B39">
+        <v>2</v>
+      </c>
+      <c r="C39">
+        <v>2</v>
+      </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40">

--- a/data/resultados.xlsx
+++ b/data/resultados.xlsx
@@ -699,82 +699,94 @@
         <v>47</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>48</v>
       </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B49">
+        <v>3</v>
+      </c>
+      <c r="C49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>50</v>
       </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B51">
+        <v>1</v>
+      </c>
+      <c r="C51">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>51</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>52</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>53</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>54</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>55</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>56</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>57</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>58</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>61</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>62</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>63</v>
       </c>

--- a/data/resultados.xlsx
+++ b/data/resultados.xlsx
@@ -703,16 +703,16 @@
       <c r="A49">
         <v>48</v>
       </c>
-      <c r="B49">
-        <v>3</v>
-      </c>
-      <c r="C49">
-        <v>1</v>
-      </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>49</v>
+      </c>
+      <c r="B50">
+        <v>3</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">

--- a/data/resultados.xlsx
+++ b/data/resultados.xlsx
@@ -750,11 +750,23 @@
       <c r="A56">
         <v>55</v>
       </c>
+      <c r="B56">
+        <v>3</v>
+      </c>
+      <c r="C56">
+        <v>0</v>
+      </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>56</v>
       </c>
+      <c r="B57">
+        <v>3</v>
+      </c>
+      <c r="C57">
+        <v>1</v>
+      </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58">
@@ -780,6 +792,12 @@
       <c r="A62">
         <v>61</v>
       </c>
+      <c r="B62">
+        <v>1</v>
+      </c>
+      <c r="C62">
+        <v>1</v>
+      </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63">
@@ -791,47 +809,53 @@
         <v>63</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>64</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>65</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>67</v>
       </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B68">
+        <v>4</v>
+      </c>
+      <c r="C68">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>68</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>70</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>71</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>72</v>
       </c>

--- a/data/resultados.xlsx
+++ b/data/resultados.xlsx
@@ -839,6 +839,12 @@
       <c r="A69">
         <v>68</v>
       </c>
+      <c r="B69">
+        <v>1</v>
+      </c>
+      <c r="C69">
+        <v>0</v>
+      </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70">

--- a/data/resultados.xlsx
+++ b/data/resultados.xlsx
@@ -409,6 +409,12 @@
       <c r="A7">
         <v>6</v>
       </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8">
@@ -446,11 +452,23 @@
       <c r="A12">
         <v>11</v>
       </c>
+      <c r="B12">
+        <v>4</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
+      <c r="B13">
+        <v>5</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14">
@@ -802,6 +820,12 @@
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>62</v>
+      </c>
+      <c r="B63">
+        <v>1</v>
+      </c>
+      <c r="C63">
+        <v>3</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">

--- a/data/resultados.xlsx
+++ b/data/resultados.xlsx
@@ -404,6 +404,12 @@
       <c r="A6">
         <v>5</v>
       </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7">

--- a/data/resultados.xlsx
+++ b/data/resultados.xlsx
@@ -507,6 +507,12 @@
       <c r="A17">
         <v>16</v>
       </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18">
@@ -531,6 +537,12 @@
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
+      </c>
+      <c r="B22">
+        <v>2</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">

--- a/data/resultados.xlsx
+++ b/data/resultados.xlsx
@@ -502,6 +502,12 @@
       <c r="A16">
         <v>15</v>
       </c>
+      <c r="B16">
+        <v>3</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17">

--- a/data/resultados.xlsx
+++ b/data/resultados.xlsx
@@ -555,6 +555,12 @@
       <c r="A23">
         <v>22</v>
       </c>
+      <c r="B23">
+        <v>0</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24">

--- a/data/resultados.xlsx
+++ b/data/resultados.xlsx
@@ -652,6 +652,12 @@
       <c r="A34">
         <v>33</v>
       </c>
+      <c r="B34">
+        <v>5</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35">

--- a/data/resultados.xlsx
+++ b/data/resultados.xlsx
@@ -598,10 +598,22 @@
       <c r="A28">
         <v>27</v>
       </c>
+      <c r="B28">
+        <v>2</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
+      </c>
+      <c r="B29">
+        <v>0</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">

--- a/data/resultados.xlsx
+++ b/data/resultados.xlsx
@@ -675,6 +675,12 @@
       <c r="A35">
         <v>34</v>
       </c>
+      <c r="B35">
+        <v>0</v>
+      </c>
+      <c r="C35">
+        <v>4</v>
+      </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36">

--- a/data/resultados.xlsx
+++ b/data/resultados.xlsx
@@ -718,6 +718,12 @@
       <c r="A40">
         <v>39</v>
       </c>
+      <c r="B40">
+        <v>0</v>
+      </c>
+      <c r="C40">
+        <v>0</v>
+      </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41">
@@ -759,6 +765,12 @@
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>45</v>
+      </c>
+      <c r="B46">
+        <v>4</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">

--- a/data/resultados.xlsx
+++ b/data/resultados.xlsx
@@ -777,6 +777,12 @@
       <c r="A47">
         <v>46</v>
       </c>
+      <c r="B47">
+        <v>2</v>
+      </c>
+      <c r="C47">
+        <v>2</v>
+      </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48">

--- a/data/resultados.xlsx
+++ b/data/resultados.xlsx
@@ -729,6 +729,12 @@
       <c r="A41">
         <v>40</v>
       </c>
+      <c r="B41">
+        <v>1</v>
+      </c>
+      <c r="C41">
+        <v>3</v>
+      </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42">

--- a/data/resultados.xlsx
+++ b/data/resultados.xlsx
@@ -826,6 +826,12 @@
       <c r="A52">
         <v>51</v>
       </c>
+      <c r="B52">
+        <v>3</v>
+      </c>
+      <c r="C52">
+        <v>0</v>
+      </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53">
@@ -867,6 +873,12 @@
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>57</v>
+      </c>
+      <c r="B58">
+        <v>2</v>
+      </c>
+      <c r="C58">
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">

--- a/data/resultados.xlsx
+++ b/data/resultados.xlsx
@@ -837,6 +837,12 @@
       <c r="A53">
         <v>52</v>
       </c>
+      <c r="B53">
+        <v>3</v>
+      </c>
+      <c r="C53">
+        <v>2</v>
+      </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54">

--- a/data/resultados.xlsx
+++ b/data/resultados.xlsx
@@ -891,6 +891,12 @@
       <c r="A59">
         <v>58</v>
       </c>
+      <c r="B59">
+        <v>1</v>
+      </c>
+      <c r="C59">
+        <v>2</v>
+      </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60">
@@ -928,6 +934,12 @@
       <c r="A64">
         <v>63</v>
       </c>
+      <c r="B64">
+        <v>5</v>
+      </c>
+      <c r="C64">
+        <v>0</v>
+      </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65">
@@ -969,6 +981,12 @@
     <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>69</v>
+      </c>
+      <c r="B70">
+        <v>0</v>
+      </c>
+      <c r="C70">
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.35">

--- a/data/resultados.xlsx
+++ b/data/resultados.xlsx
@@ -993,6 +993,12 @@
       <c r="A71">
         <v>70</v>
       </c>
+      <c r="B71">
+        <v>0</v>
+      </c>
+      <c r="C71">
+        <v>1</v>
+      </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72">

--- a/data/resultados.xlsx
+++ b/data/resultados.xlsx
@@ -426,11 +426,23 @@
       <c r="A8">
         <v>7</v>
       </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
+      <c r="B9">
+        <v>3</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10">
@@ -524,11 +536,23 @@
       <c r="A18">
         <v>17</v>
       </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="C18">
+        <v>3</v>
+      </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
+      <c r="B19">
+        <v>4</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20">
@@ -944,6 +968,12 @@
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>64</v>
+      </c>
+      <c r="B65">
+        <v>1</v>
+      </c>
+      <c r="C65">
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">

--- a/data/resultados.xlsx
+++ b/data/resultados.xlsx
@@ -394,11 +394,23 @@
       <c r="A4">
         <v>3</v>
       </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6">
@@ -612,11 +624,23 @@
       <c r="A26">
         <v>25</v>
       </c>
+      <c r="B26">
+        <v>2</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
+      <c r="B27">
+        <v>0</v>
+      </c>
+      <c r="C27">
+        <v>2</v>
+      </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28">
@@ -710,10 +734,22 @@
       <c r="A36">
         <v>35</v>
       </c>
+      <c r="B36">
+        <v>1</v>
+      </c>
+      <c r="C36">
+        <v>3</v>
+      </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
+      </c>
+      <c r="B37">
+        <v>1</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">

--- a/data/resultados.xlsx
+++ b/data/resultados.xlsx
@@ -570,11 +570,23 @@
       <c r="A20">
         <v>19</v>
       </c>
+      <c r="B20">
+        <v>3</v>
+      </c>
+      <c r="C20">
+        <v>2</v>
+      </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22">
@@ -908,10 +920,22 @@
       <c r="A54">
         <v>53</v>
       </c>
+      <c r="B54">
+        <v>4</v>
+      </c>
+      <c r="C54">
+        <v>1</v>
+      </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>54</v>
+      </c>
+      <c r="B55">
+        <v>5</v>
+      </c>
+      <c r="C55">
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">

--- a/data/resultados.xlsx
+++ b/data/resultados.xlsx
@@ -812,11 +812,23 @@
       <c r="A42">
         <v>41</v>
       </c>
+      <c r="B42">
+        <v>1</v>
+      </c>
+      <c r="C42">
+        <v>5</v>
+      </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>42</v>
       </c>
+      <c r="B43">
+        <v>1</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44">
@@ -866,10 +878,22 @@
       <c r="A48">
         <v>47</v>
       </c>
+      <c r="B48">
+        <v>0</v>
+      </c>
+      <c r="C48">
+        <v>1</v>
+      </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>48</v>
+      </c>
+      <c r="B49">
+        <v>0</v>
+      </c>
+      <c r="C49">
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">

--- a/data/resultados.xlsx
+++ b/data/resultados.xlsx
@@ -1064,11 +1064,23 @@
       <c r="A66">
         <v>65</v>
       </c>
+      <c r="B66">
+        <v>0</v>
+      </c>
+      <c r="C66">
+        <v>0</v>
+      </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>66</v>
       </c>
+      <c r="B67">
+        <v>3</v>
+      </c>
+      <c r="C67">
+        <v>1</v>
+      </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68">
@@ -1118,10 +1130,22 @@
       <c r="A72">
         <v>71</v>
       </c>
+      <c r="B72">
+        <v>0</v>
+      </c>
+      <c r="C72">
+        <v>2</v>
+      </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>72</v>
+      </c>
+      <c r="B73">
+        <v>2</v>
+      </c>
+      <c r="C73">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/resultados.xlsx
+++ b/data/resultados.xlsx
@@ -1010,10 +1010,22 @@
       <c r="A60">
         <v>59</v>
       </c>
+      <c r="B60">
+        <v>1</v>
+      </c>
+      <c r="C60">
+        <v>3</v>
+      </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>60</v>
+      </c>
+      <c r="B61">
+        <v>3</v>
+      </c>
+      <c r="C61">
+        <v>3</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
